--- a/research/traditional_assets/database/data/spain/spain_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.185</v>
+        <v>0.197</v>
       </c>
       <c r="E2">
-        <v>0.04714999999999999</v>
+        <v>0.0735</v>
       </c>
       <c r="G2">
-        <v>0.0003100303951367781</v>
+        <v>0.0004055390702274975</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -606,91 +606,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>79.5</v>
+        <v>55.1</v>
       </c>
       <c r="L2">
-        <v>0.1610942249240122</v>
+        <v>0.1816683151994725</v>
       </c>
       <c r="M2">
-        <v>38.256</v>
+        <v>36.999</v>
       </c>
       <c r="N2">
-        <v>0.03386685552407932</v>
+        <v>0.07442969221484609</v>
       </c>
       <c r="O2">
-        <v>0.4812075471698113</v>
+        <v>0.6714882032667876</v>
       </c>
       <c r="P2">
-        <v>37.5</v>
+        <v>36.3</v>
       </c>
       <c r="Q2">
-        <v>0.03319759206798867</v>
+        <v>0.07302353651176825</v>
       </c>
       <c r="R2">
-        <v>0.4716981132075472</v>
+        <v>0.6588021778584391</v>
       </c>
       <c r="S2">
-        <v>0.7560000000000002</v>
+        <v>0.6989999999999981</v>
       </c>
       <c r="T2">
-        <v>0.0197616060225847</v>
+        <v>0.01889240249736474</v>
       </c>
       <c r="U2">
-        <v>1249.4</v>
+        <v>151.8</v>
       </c>
       <c r="V2">
-        <v>1.106055240793201</v>
+        <v>0.3053711526855764</v>
       </c>
       <c r="W2">
-        <v>0.1989371764305085</v>
+        <v>0.1762635956493922</v>
       </c>
       <c r="X2">
-        <v>0.04086517244291367</v>
+        <v>0.0816490261857904</v>
       </c>
       <c r="Y2">
-        <v>0.1580720039875948</v>
+        <v>0.09461456946360178</v>
       </c>
       <c r="Z2">
-        <v>-0.699048104708482</v>
+        <v>2.311737804878048</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04057085132164832</v>
+        <v>0.07852586460072704</v>
       </c>
       <c r="AC2">
-        <v>-0.04057085132164832</v>
+        <v>-0.07852586460072704</v>
       </c>
       <c r="AD2">
-        <v>30.1</v>
+        <v>54.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>30.1</v>
+        <v>54.7</v>
       </c>
       <c r="AG2">
-        <v>-1219.3</v>
+        <v>-97.10000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.02595498835905838</v>
+        <v>0.09913011960855382</v>
       </c>
       <c r="AI2">
-        <v>0.05337825855648165</v>
+        <v>0.125545099839339</v>
       </c>
       <c r="AJ2">
-        <v>13.59308807134893</v>
+        <v>-0.24275</v>
       </c>
       <c r="AK2">
-        <v>1.778701677607586</v>
+        <v>-0.3420218386755901</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-2.85</v>
+        <v>-0.751</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Renta 4 Banco, S.A. (BME:R4)</t>
+          <t>Alantra Partners, S.A. (BME:ALNT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07000000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="E3">
-        <v>0.164</v>
+        <v>0.0735</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.0004055390702274975</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -731,212 +731,93 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>28.2</v>
+        <v>55.1</v>
       </c>
       <c r="L3">
-        <v>0.1340941512125535</v>
+        <v>0.1816683151994725</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>36.999</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.07442969221484609</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.6714882032667876</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>36.3</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07302353651176825</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.6588021778584391</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.6989999999999981</v>
+      </c>
+      <c r="T3">
+        <v>0.01889240249736474</v>
       </c>
       <c r="U3">
-        <v>1114.6</v>
+        <v>151.8</v>
       </c>
       <c r="V3">
-        <v>2.399569429494079</v>
+        <v>0.3053711526855764</v>
       </c>
       <c r="W3">
-        <v>0.2134746404239213</v>
+        <v>0.1762635956493922</v>
       </c>
       <c r="X3">
-        <v>0.04043520532502727</v>
+        <v>0.0816490261857904</v>
       </c>
       <c r="Y3">
-        <v>0.173039435098894</v>
+        <v>0.09461456946360178</v>
       </c>
       <c r="Z3">
-        <v>-0.2486520998864926</v>
+        <v>2.311737804878048</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04043520532502727</v>
+        <v>0.07852586460072704</v>
       </c>
       <c r="AC3">
-        <v>-0.04043520532502727</v>
+        <v>-0.07852586460072704</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>54.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>54.7</v>
       </c>
       <c r="AG3">
-        <v>-1114.6</v>
+        <v>-97.10000000000001</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.09913011960855382</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.125545099839339</v>
       </c>
       <c r="AJ3">
-        <v>1.714505460698354</v>
+        <v>-0.24275</v>
       </c>
       <c r="AK3">
-        <v>1.167120418848168</v>
+        <v>-0.3420218386755901</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Alantra Partners, S.A. (BME:ALNT)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.3</v>
-      </c>
-      <c r="E4">
-        <v>-0.0697</v>
-      </c>
-      <c r="G4">
-        <v>0.0005402542372881356</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>51.3</v>
-      </c>
-      <c r="L4">
-        <v>0.1811440677966102</v>
-      </c>
-      <c r="M4">
-        <v>38.256</v>
-      </c>
-      <c r="N4">
-        <v>0.0575191700496166</v>
-      </c>
-      <c r="O4">
-        <v>0.7457309941520468</v>
-      </c>
-      <c r="P4">
-        <v>37.5</v>
-      </c>
-      <c r="Q4">
-        <v>0.05638249887235002</v>
-      </c>
-      <c r="R4">
-        <v>0.7309941520467836</v>
-      </c>
-      <c r="S4">
-        <v>0.7560000000000002</v>
-      </c>
-      <c r="T4">
-        <v>0.0197616060225847</v>
-      </c>
-      <c r="U4">
-        <v>134.8</v>
-      </c>
-      <c r="V4">
-        <v>0.2026762892798075</v>
-      </c>
-      <c r="W4">
-        <v>0.1843997124370956</v>
-      </c>
-      <c r="X4">
-        <v>0.04129513956080007</v>
-      </c>
-      <c r="Y4">
-        <v>0.1431045728762955</v>
-      </c>
-      <c r="Z4">
-        <v>2.025751072961374</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.04070649731826937</v>
-      </c>
-      <c r="AC4">
-        <v>-0.04070649731826937</v>
-      </c>
-      <c r="AD4">
-        <v>30.1</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>30.1</v>
-      </c>
-      <c r="AG4">
-        <v>-104.7</v>
-      </c>
-      <c r="AH4">
-        <v>0.04329689298043728</v>
-      </c>
-      <c r="AI4">
-        <v>0.07444966608953747</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.1868308351177731</v>
-      </c>
-      <c r="AK4">
-        <v>-0.3884972170686457</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-2.85</v>
-      </c>
-      <c r="AQ4">
+        <v>-0.751</v>
+      </c>
+      <c r="AQ3">
         <v>-0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/spain/spain_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_brokerage_investment_banking.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.197</v>
+        <v>0.0619</v>
       </c>
       <c r="E2">
-        <v>0.0735</v>
+        <v>-0.0413</v>
       </c>
       <c r="G2">
-        <v>0.0004055390702274975</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -606,91 +606,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>55.1</v>
+        <v>24.3</v>
       </c>
       <c r="L2">
-        <v>0.1816683151994725</v>
+        <v>0.1117241379310345</v>
       </c>
       <c r="M2">
-        <v>36.999</v>
+        <v>34.6</v>
       </c>
       <c r="N2">
-        <v>0.07442969221484609</v>
+        <v>0.09608442099416828</v>
       </c>
       <c r="O2">
-        <v>0.6714882032667876</v>
+        <v>1.423868312757202</v>
       </c>
       <c r="P2">
-        <v>36.3</v>
+        <v>34.6</v>
       </c>
       <c r="Q2">
-        <v>0.07302353651176825</v>
+        <v>0.09608442099416828</v>
       </c>
       <c r="R2">
-        <v>0.6588021778584391</v>
+        <v>1.423868312757202</v>
       </c>
       <c r="S2">
-        <v>0.6989999999999981</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.01889240249736474</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>151.8</v>
+        <v>105.9</v>
       </c>
       <c r="V2">
-        <v>0.3053711526855764</v>
+        <v>0.2940849763954457</v>
       </c>
       <c r="W2">
-        <v>0.1762635956493922</v>
+        <v>0.0802775024777007</v>
       </c>
       <c r="X2">
-        <v>0.0816490261857904</v>
+        <v>0.0685898192142788</v>
       </c>
       <c r="Y2">
-        <v>0.09461456946360178</v>
+        <v>0.0116876832634219</v>
       </c>
       <c r="Z2">
-        <v>2.311737804878048</v>
+        <v>2.74968394437421</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07852586460072704</v>
+        <v>0.06582728961919691</v>
       </c>
       <c r="AC2">
-        <v>-0.07852586460072704</v>
+        <v>-0.06582728961919691</v>
       </c>
       <c r="AD2">
-        <v>54.7</v>
+        <v>52.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>54.7</v>
+        <v>52.4</v>
       </c>
       <c r="AG2">
-        <v>-97.10000000000001</v>
+        <v>-53.50000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.09913011960855382</v>
+        <v>0.127030303030303</v>
       </c>
       <c r="AI2">
-        <v>0.125545099839339</v>
+        <v>0.1146608315098468</v>
       </c>
       <c r="AJ2">
-        <v>-0.24275</v>
+        <v>-0.1744944553163731</v>
       </c>
       <c r="AK2">
-        <v>-0.3420218386755901</v>
+        <v>-0.1523782398177158</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.751</v>
+        <v>-0.826</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.197</v>
+        <v>0.0619</v>
       </c>
       <c r="E3">
-        <v>0.0735</v>
+        <v>-0.0413</v>
       </c>
       <c r="G3">
-        <v>0.0004055390702274975</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -731,91 +731,91 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>55.1</v>
+        <v>24.3</v>
       </c>
       <c r="L3">
-        <v>0.1816683151994725</v>
+        <v>0.1117241379310345</v>
       </c>
       <c r="M3">
-        <v>36.999</v>
+        <v>34.6</v>
       </c>
       <c r="N3">
-        <v>0.07442969221484609</v>
+        <v>0.09608442099416828</v>
       </c>
       <c r="O3">
-        <v>0.6714882032667876</v>
+        <v>1.423868312757202</v>
       </c>
       <c r="P3">
-        <v>36.3</v>
+        <v>34.6</v>
       </c>
       <c r="Q3">
-        <v>0.07302353651176825</v>
+        <v>0.09608442099416828</v>
       </c>
       <c r="R3">
-        <v>0.6588021778584391</v>
+        <v>1.423868312757202</v>
       </c>
       <c r="S3">
-        <v>0.6989999999999981</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.01889240249736474</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>151.8</v>
+        <v>105.9</v>
       </c>
       <c r="V3">
-        <v>0.3053711526855764</v>
+        <v>0.2940849763954457</v>
       </c>
       <c r="W3">
-        <v>0.1762635956493922</v>
+        <v>0.0802775024777007</v>
       </c>
       <c r="X3">
-        <v>0.0816490261857904</v>
+        <v>0.0685898192142788</v>
       </c>
       <c r="Y3">
-        <v>0.09461456946360178</v>
+        <v>0.0116876832634219</v>
       </c>
       <c r="Z3">
-        <v>2.311737804878048</v>
+        <v>2.74968394437421</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07852586460072704</v>
+        <v>0.06582728961919691</v>
       </c>
       <c r="AC3">
-        <v>-0.07852586460072704</v>
+        <v>-0.06582728961919691</v>
       </c>
       <c r="AD3">
-        <v>54.7</v>
+        <v>52.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>54.7</v>
+        <v>52.4</v>
       </c>
       <c r="AG3">
-        <v>-97.10000000000001</v>
+        <v>-53.50000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.09913011960855382</v>
+        <v>0.127030303030303</v>
       </c>
       <c r="AI3">
-        <v>0.125545099839339</v>
+        <v>0.1146608315098468</v>
       </c>
       <c r="AJ3">
-        <v>-0.24275</v>
+        <v>-0.1744944553163731</v>
       </c>
       <c r="AK3">
-        <v>-0.3420218386755901</v>
+        <v>-0.1523782398177158</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.751</v>
+        <v>-0.826</v>
       </c>
       <c r="AQ3">
         <v>-0</v>
